--- a/2024AIDataScienceGNRGeneral/Attendance2.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D100761-A8A2-4B88-ADB4-DC936E491AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABD565F-6661-4B64-AC73-519968FFCB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>Online</t>
   </si>
 </sst>
 </file>
@@ -437,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA36"/>
+  <dimension ref="A1:AB37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -450,7 +453,7 @@
     <col min="27" max="27" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -529,8 +532,11 @@
       <c r="AA1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB1" s="1">
+        <v>45689</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -609,8 +615,11 @@
       <c r="Z2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -692,8 +701,11 @@
       <c r="AA3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -775,8 +787,11 @@
       <c r="AA4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -855,8 +870,11 @@
       <c r="Z5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -938,8 +956,11 @@
       <c r="AA6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1021,8 +1042,11 @@
       <c r="AA7" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1104,8 +1128,11 @@
       <c r="AA8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1184,8 +1211,11 @@
       <c r="Z9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>24</v>
       </c>
@@ -1267,8 +1297,11 @@
       <c r="AA10" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1350,8 +1383,11 @@
       <c r="AA11" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1433,8 +1469,11 @@
       <c r="AA12" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1516,8 +1555,11 @@
       <c r="AA13" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1599,8 +1641,11 @@
       <c r="AA14" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1682,8 +1727,11 @@
       <c r="AA15" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>25</v>
       </c>
@@ -1762,8 +1810,11 @@
       <c r="Z16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1842,8 +1893,11 @@
       <c r="Z17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="AB17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -1925,226 +1979,302 @@
       <c r="AA18" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="AB18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="D20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>22</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <f>COUNTIF(C2:Z2, "O") + COUNTIF(C2:Z2, "P")</f>
         <v>3</v>
       </c>
-      <c r="C20">
-        <f>ROUND(B20*100/24, 1)</f>
+      <c r="C21">
+        <f>ROUND(B21*100/24, 1)</f>
         <v>12.5</v>
       </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="D21">
+        <f>COUNTIF(C2:Z2, "O")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>10</v>
       </c>
-      <c r="B21">
-        <f t="shared" ref="B21:B36" si="0">COUNTIF(C3:Z3, "O") + COUNTIF(C3:Z3, "P")</f>
-        <v>21</v>
-      </c>
-      <c r="C21">
-        <f t="shared" ref="C21:C36" si="1">ROUND(B21*100/24, 1)</f>
+      <c r="B22">
+        <f>COUNTIF(C3:Z3, "O") + COUNTIF(C3:Z3, "P")</f>
+        <v>21</v>
+      </c>
+      <c r="C22">
+        <f t="shared" ref="C22:C37" si="0">ROUND(B22*100/24, 1)</f>
         <v>87.5</v>
       </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="D22">
+        <f>COUNTIF(C3:Z3, "O")</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>1</v>
       </c>
-      <c r="B22">
+      <c r="B23">
+        <f>COUNTIF(C4:Z4, "O") + COUNTIF(C4:Z4, "P")</f>
+        <v>17</v>
+      </c>
+      <c r="C23">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C22">
+        <v>70.8</v>
+      </c>
+      <c r="D23">
+        <f t="shared" ref="D23:D37" si="1">COUNTIF(C4:Z4, "O")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24">
+        <f>COUNTIF(C5:Z5, "O") + COUNTIF(C5:Z5, "P")</f>
+        <v>10</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>41.7</v>
+      </c>
+      <c r="D24">
         <f t="shared" si="1"/>
-        <v>70.8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25">
+        <f>COUNTIF(C6:Z6, "O") + COUNTIF(C6:Z6, "P")</f>
+        <v>21</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>87.5</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <f>COUNTIF(C7:Z7, "O") + COUNTIF(C7:Z7, "P")</f>
+        <v>19</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>79.2</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <f>COUNTIF(C8:Z8, "O") + COUNTIF(C8:Z8, "P")</f>
+        <v>18</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="B23">
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <f>COUNTIF(C9:Z9, "O") + COUNTIF(C9:Z9, "P")</f>
+        <v>22</v>
+      </c>
+      <c r="C28">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C23">
+        <v>91.7</v>
+      </c>
+      <c r="D28">
         <f t="shared" si="1"/>
-        <v>41.7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29">
+        <f>COUNTIF(C10:Z10, "O") + COUNTIF(C10:Z10, "P")</f>
+        <v>18</v>
+      </c>
+      <c r="C29">
         <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C24">
+        <v>75</v>
+      </c>
+      <c r="D29">
         <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30">
+        <f>COUNTIF(C11:Z11, "O") + COUNTIF(C11:Z11, "P")</f>
+        <v>22</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="0"/>
+        <v>91.7</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31">
+        <f>COUNTIF(C12:Z12, "O") + COUNTIF(C12:Z12, "P")</f>
+        <v>21</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="0"/>
         <v>87.5</v>
       </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25">
+      <c r="D31">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32">
+        <f>COUNTIF(C13:Z13, "O") + COUNTIF(C13:Z13, "P")</f>
+        <v>22</v>
+      </c>
+      <c r="C32">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C25">
+        <v>91.7</v>
+      </c>
+      <c r="D32">
         <f t="shared" si="1"/>
-        <v>79.2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33">
+        <f>COUNTIF(C14:Z14, "O") + COUNTIF(C14:Z14, "P")</f>
+        <v>16</v>
+      </c>
+      <c r="C33">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="C26">
+        <v>66.7</v>
+      </c>
+      <c r="D33">
         <f t="shared" si="1"/>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34">
+        <f>COUNTIF(C15:Z15, "O") + COUNTIF(C15:Z15, "P")</f>
+        <v>22</v>
+      </c>
+      <c r="C34">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="C27">
+        <v>91.7</v>
+      </c>
+      <c r="D34">
         <f t="shared" si="1"/>
-        <v>91.7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35">
+        <f>COUNTIF(C16:Z16, "O") + COUNTIF(C16:Z16, "P")</f>
+        <v>1</v>
+      </c>
+      <c r="C35">
         <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="C28">
+        <v>4.2</v>
+      </c>
+      <c r="D35">
         <f t="shared" si="1"/>
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36">
+        <f>COUNTIF(C17:Z17, "O") + COUNTIF(C17:Z17, "P")</f>
+        <v>6</v>
+      </c>
+      <c r="C36">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37">
+        <f>COUNTIF(C18:Z18, "O") + COUNTIF(C18:Z18, "P")</f>
         <v>13</v>
       </c>
-      <c r="B29">
+      <c r="C37">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="C29">
+        <v>54.2</v>
+      </c>
+      <c r="D37">
         <f t="shared" si="1"/>
-        <v>91.7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C30">
-        <f t="shared" si="1"/>
-        <v>87.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="C31">
-        <f t="shared" si="1"/>
-        <v>91.7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C32">
-        <f t="shared" si="1"/>
-        <v>66.7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="C33">
-        <f t="shared" si="1"/>
-        <v>91.7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="C34">
-        <f t="shared" si="1"/>
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C35">
-        <f t="shared" si="1"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B36">
-        <f t="shared" si="0"/>
         <v>13</v>
-      </c>
-      <c r="C36">
-        <f t="shared" si="1"/>
-        <v>54.2</v>
       </c>
     </row>
   </sheetData>

--- a/2024AIDataScienceGNRGeneral/Attendance2.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABD565F-6661-4B64-AC73-519968FFCB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF76CB89-D7C1-44C2-BF92-DF1C4F6FDF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -453,7 +453,7 @@
     <col min="27" max="27" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -535,8 +535,11 @@
       <c r="AB1" s="1">
         <v>45689</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC1" s="1">
+        <v>45696</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -618,8 +621,11 @@
       <c r="AB2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -704,8 +710,11 @@
       <c r="AB3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -790,10 +799,13 @@
       <c r="AB4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -802,22 +814,22 @@
         <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J5" t="s">
         <v>9</v>
@@ -826,16 +838,16 @@
         <v>21</v>
       </c>
       <c r="L5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="N5" t="s">
         <v>9</v>
       </c>
       <c r="O5" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="P5" t="s">
         <v>9</v>
@@ -844,39 +856,45 @@
         <v>9</v>
       </c>
       <c r="R5" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="S5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="T5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="U5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="V5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="W5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="X5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Y5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Z5" t="s">
-        <v>21</v>
+        <v>9</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>29</v>
       </c>
       <c r="AB5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
@@ -906,19 +924,19 @@
         <v>9</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M6" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="N6" t="s">
         <v>9</v>
       </c>
       <c r="O6" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="P6" t="s">
         <v>9</v>
@@ -927,7 +945,7 @@
         <v>9</v>
       </c>
       <c r="R6" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="S6" t="s">
         <v>9</v>
@@ -942,16 +960,16 @@
         <v>9</v>
       </c>
       <c r="W6" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="X6" t="s">
         <v>9</v>
       </c>
       <c r="Y6" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Z6" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="s">
         <v>29</v>
@@ -959,10 +977,13 @@
       <c r="AB6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
@@ -992,13 +1013,13 @@
         <v>9</v>
       </c>
       <c r="K7" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M7" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="N7" t="s">
         <v>9</v>
@@ -1007,19 +1028,19 @@
         <v>9</v>
       </c>
       <c r="P7" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="R7" t="s">
         <v>9</v>
       </c>
       <c r="S7" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="T7" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="U7" t="s">
         <v>9</v>
@@ -1031,13 +1052,13 @@
         <v>21</v>
       </c>
       <c r="X7" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Z7" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AA7" t="s">
         <v>29</v>
@@ -1045,188 +1066,197 @@
       <c r="AB7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>9</v>
+      </c>
+      <c r="R8" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" t="s">
+        <v>9</v>
+      </c>
+      <c r="U8" t="s">
+        <v>9</v>
+      </c>
+      <c r="V8" t="s">
+        <v>21</v>
+      </c>
+      <c r="W8" t="s">
+        <v>9</v>
+      </c>
+      <c r="X8" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" t="s">
-        <v>15</v>
-      </c>
-      <c r="M8" t="s">
-        <v>9</v>
-      </c>
-      <c r="N8" t="s">
-        <v>9</v>
-      </c>
-      <c r="O8" t="s">
-        <v>9</v>
-      </c>
-      <c r="P8" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>21</v>
-      </c>
-      <c r="R8" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" t="s">
-        <v>21</v>
-      </c>
-      <c r="T8" t="s">
-        <v>21</v>
-      </c>
-      <c r="U8" t="s">
-        <v>9</v>
-      </c>
-      <c r="V8" t="s">
-        <v>9</v>
-      </c>
-      <c r="W8" t="s">
-        <v>21</v>
-      </c>
-      <c r="X8" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA8" t="s">
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" t="s">
+        <v>9</v>
+      </c>
+      <c r="N9" t="s">
+        <v>9</v>
+      </c>
+      <c r="O9" t="s">
+        <v>9</v>
+      </c>
+      <c r="P9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>9</v>
+      </c>
+      <c r="R9" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" t="s">
+        <v>9</v>
+      </c>
+      <c r="T9" t="s">
+        <v>21</v>
+      </c>
+      <c r="U9" t="s">
+        <v>9</v>
+      </c>
+      <c r="V9" t="s">
+        <v>21</v>
+      </c>
+      <c r="W9" t="s">
+        <v>21</v>
+      </c>
+      <c r="X9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA9" t="s">
         <v>29</v>
       </c>
-      <c r="AB8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" t="s">
-        <v>9</v>
-      </c>
-      <c r="N9" t="s">
-        <v>9</v>
-      </c>
-      <c r="O9" t="s">
-        <v>9</v>
-      </c>
-      <c r="P9" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>9</v>
-      </c>
-      <c r="R9" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" t="s">
-        <v>9</v>
-      </c>
-      <c r="T9" t="s">
-        <v>9</v>
-      </c>
-      <c r="U9" t="s">
-        <v>9</v>
-      </c>
-      <c r="V9" t="s">
-        <v>21</v>
-      </c>
-      <c r="W9" t="s">
-        <v>9</v>
-      </c>
-      <c r="X9" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y9" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>9</v>
-      </c>
       <c r="AB9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1247,7 +1277,7 @@
         <v>9</v>
       </c>
       <c r="K10" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -1262,7 +1292,7 @@
         <v>9</v>
       </c>
       <c r="P10" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q10" t="s">
         <v>9</v>
@@ -1274,13 +1304,13 @@
         <v>9</v>
       </c>
       <c r="T10" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="U10" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="V10" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="W10" t="s">
         <v>21</v>
@@ -1300,10 +1330,13 @@
       <c r="AB10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -1330,7 +1363,7 @@
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K11" t="s">
         <v>9</v>
@@ -1348,13 +1381,13 @@
         <v>9</v>
       </c>
       <c r="P11" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="s">
         <v>9</v>
       </c>
       <c r="R11" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="S11" t="s">
         <v>9</v>
@@ -1363,7 +1396,7 @@
         <v>9</v>
       </c>
       <c r="U11" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="V11" t="s">
         <v>9</v>
@@ -1386,16 +1419,19 @@
       <c r="AB11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
@@ -1407,7 +1443,7 @@
         <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H12" t="s">
         <v>9</v>
@@ -1416,7 +1452,7 @@
         <v>9</v>
       </c>
       <c r="J12" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K12" t="s">
         <v>9</v>
@@ -1440,7 +1476,7 @@
         <v>9</v>
       </c>
       <c r="R12" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="S12" t="s">
         <v>9</v>
@@ -1472,10 +1508,13 @@
       <c r="AB12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
@@ -1490,28 +1529,28 @@
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H13" t="s">
         <v>9</v>
       </c>
       <c r="I13" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K13" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M13" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="N13" t="s">
         <v>9</v>
@@ -1520,7 +1559,7 @@
         <v>9</v>
       </c>
       <c r="P13" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Q13" t="s">
         <v>9</v>
@@ -1532,7 +1571,7 @@
         <v>9</v>
       </c>
       <c r="T13" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="U13" t="s">
         <v>9</v>
@@ -1544,7 +1583,7 @@
         <v>21</v>
       </c>
       <c r="X13" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="s">
         <v>9</v>
@@ -1558,10 +1597,13 @@
       <c r="AB13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
@@ -1576,7 +1618,7 @@
         <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G14" t="s">
         <v>9</v>
@@ -1585,7 +1627,7 @@
         <v>9</v>
       </c>
       <c r="I14" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J14" t="s">
         <v>21</v>
@@ -1594,7 +1636,7 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M14" t="s">
         <v>15</v>
@@ -1603,10 +1645,10 @@
         <v>9</v>
       </c>
       <c r="O14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P14" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q14" t="s">
         <v>9</v>
@@ -1618,25 +1660,25 @@
         <v>9</v>
       </c>
       <c r="T14" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="U14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="V14" t="s">
         <v>9</v>
       </c>
       <c r="W14" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="X14" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="s">
         <v>9</v>
       </c>
       <c r="Z14" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="s">
         <v>29</v>
@@ -1644,209 +1686,215 @@
       <c r="AB14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="AC14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B15" t="s">
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H15" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I15" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J15" t="s">
         <v>21</v>
       </c>
       <c r="K15" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L15" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M15" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N15" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="O15" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="P15" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Q15" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="R15" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="S15" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="T15" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="U15" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="V15" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="W15" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="X15" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="s">
         <v>21</v>
       </c>
-      <c r="AA15" t="s">
-        <v>29</v>
-      </c>
       <c r="AB15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
       </c>
       <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>21</v>
+      </c>
+      <c r="K16" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M16" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" t="s">
+        <v>21</v>
+      </c>
+      <c r="P16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>21</v>
+      </c>
+      <c r="R16" t="s">
+        <v>21</v>
+      </c>
+      <c r="S16" t="s">
+        <v>21</v>
+      </c>
+      <c r="T16" t="s">
+        <v>21</v>
+      </c>
+      <c r="U16" t="s">
+        <v>21</v>
+      </c>
+      <c r="V16" t="s">
+        <v>21</v>
+      </c>
+      <c r="W16" t="s">
+        <v>21</v>
+      </c>
+      <c r="X16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
         <v>20</v>
       </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>21</v>
-      </c>
-      <c r="G16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" t="s">
-        <v>21</v>
-      </c>
-      <c r="I16" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" t="s">
-        <v>21</v>
-      </c>
-      <c r="P16" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>21</v>
-      </c>
-      <c r="R16" t="s">
-        <v>21</v>
-      </c>
-      <c r="S16" t="s">
-        <v>21</v>
-      </c>
-      <c r="T16" t="s">
-        <v>21</v>
-      </c>
-      <c r="U16" t="s">
-        <v>21</v>
-      </c>
-      <c r="V16" t="s">
-        <v>21</v>
-      </c>
-      <c r="W16" t="s">
-        <v>21</v>
-      </c>
-      <c r="X16" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J17" t="s">
         <v>21</v>
       </c>
       <c r="K17" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L17" t="s">
         <v>21</v>
@@ -1861,31 +1909,31 @@
         <v>21</v>
       </c>
       <c r="P17" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q17" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="R17" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="S17" t="s">
         <v>21</v>
       </c>
       <c r="T17" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="U17" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="V17" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="W17" t="s">
         <v>21</v>
       </c>
       <c r="X17" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="s">
         <v>21</v>
@@ -1893,393 +1941,313 @@
       <c r="Z17" t="s">
         <v>21</v>
       </c>
+      <c r="AA17" t="s">
+        <v>29</v>
+      </c>
       <c r="AB17" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" t="s">
-        <v>15</v>
-      </c>
-      <c r="J18" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" t="s">
-        <v>21</v>
-      </c>
-      <c r="O18" t="s">
-        <v>21</v>
-      </c>
-      <c r="P18" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>15</v>
-      </c>
-      <c r="R18" t="s">
-        <v>15</v>
-      </c>
-      <c r="S18" t="s">
-        <v>21</v>
-      </c>
-      <c r="T18" t="s">
-        <v>15</v>
-      </c>
-      <c r="U18" t="s">
-        <v>15</v>
-      </c>
-      <c r="V18" t="s">
-        <v>15</v>
-      </c>
-      <c r="W18" t="s">
-        <v>21</v>
-      </c>
-      <c r="X18" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="D20" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>22</v>
       </c>
-      <c r="B21">
+      <c r="B20">
         <f>COUNTIF(C2:Z2, "O") + COUNTIF(C2:Z2, "P")</f>
         <v>3</v>
       </c>
-      <c r="C21">
-        <f>ROUND(B21*100/24, 1)</f>
+      <c r="C20">
+        <f>ROUND(B20*100/24, 1)</f>
         <v>12.5</v>
       </c>
-      <c r="D21">
+      <c r="D20">
         <f>COUNTIF(C2:Z2, "O")</f>
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>10</v>
       </c>
-      <c r="B22">
+      <c r="B21">
         <f>COUNTIF(C3:Z3, "O") + COUNTIF(C3:Z3, "P")</f>
         <v>21</v>
       </c>
-      <c r="C22">
-        <f t="shared" ref="C22:C37" si="0">ROUND(B22*100/24, 1)</f>
+      <c r="C21">
+        <f t="shared" ref="C21:C36" si="0">ROUND(B21*100/24, 1)</f>
         <v>87.5</v>
       </c>
-      <c r="D22">
+      <c r="D21">
         <f>COUNTIF(C3:Z3, "O")</f>
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>1</v>
       </c>
-      <c r="B23">
+      <c r="B22">
         <f>COUNTIF(C4:Z4, "O") + COUNTIF(C4:Z4, "P")</f>
         <v>17</v>
       </c>
-      <c r="C23">
+      <c r="C22">
         <f t="shared" si="0"/>
         <v>70.8</v>
       </c>
-      <c r="D23">
-        <f t="shared" ref="D23:D37" si="1">COUNTIF(C4:Z4, "O")</f>
+      <c r="D22">
+        <f>COUNTIF(C4:Z4, "O")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" t="e">
+        <f>COUNTIF(#REF!, "O") + COUNTIF(#REF!, "P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C23" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="D23" t="e">
+        <f>COUNTIF(#REF!, "O")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B24">
-        <f>COUNTIF(C5:Z5, "O") + COUNTIF(C5:Z5, "P")</f>
-        <v>10</v>
+        <f t="shared" ref="B24:B36" si="1">COUNTIF(C5:Z5, "O") + COUNTIF(C5:Z5, "P")</f>
+        <v>21</v>
       </c>
       <c r="C24">
         <f t="shared" si="0"/>
-        <v>41.7</v>
+        <v>87.5</v>
       </c>
       <c r="D24">
+        <f t="shared" ref="D24:D36" si="2">COUNTIF(C5:Z5, "O")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25">
-        <f>COUNTIF(C6:Z6, "O") + COUNTIF(C6:Z6, "P")</f>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C25">
         <f t="shared" si="0"/>
+        <v>79.2</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>91.7</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="0"/>
+        <v>91.7</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="0"/>
         <v>87.5</v>
       </c>
-      <c r="D25">
+      <c r="D30">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="0"/>
+        <v>91.7</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="0"/>
+        <v>66.7</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33">
+        <f t="shared" si="1"/>
+        <v>22</v>
+      </c>
+      <c r="C33">
+        <f t="shared" si="0"/>
+        <v>91.7</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26">
-        <f>COUNTIF(C7:Z7, "O") + COUNTIF(C7:Z7, "P")</f>
-        <v>19</v>
-      </c>
-      <c r="C26">
-        <f t="shared" si="0"/>
-        <v>79.2</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27">
-        <f>COUNTIF(C8:Z8, "O") + COUNTIF(C8:Z8, "P")</f>
-        <v>18</v>
-      </c>
-      <c r="C27">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="D27">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28">
-        <f>COUNTIF(C9:Z9, "O") + COUNTIF(C9:Z9, "P")</f>
-        <v>22</v>
-      </c>
-      <c r="C28">
-        <f t="shared" si="0"/>
-        <v>91.7</v>
-      </c>
-      <c r="D28">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29">
-        <f>COUNTIF(C10:Z10, "O") + COUNTIF(C10:Z10, "P")</f>
-        <v>18</v>
-      </c>
-      <c r="C29">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="D29">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30">
-        <f>COUNTIF(C11:Z11, "O") + COUNTIF(C11:Z11, "P")</f>
-        <v>22</v>
-      </c>
-      <c r="C30">
-        <f t="shared" si="0"/>
-        <v>91.7</v>
-      </c>
-      <c r="D30">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31">
-        <f>COUNTIF(C12:Z12, "O") + COUNTIF(C12:Z12, "P")</f>
-        <v>21</v>
-      </c>
-      <c r="C31">
-        <f t="shared" si="0"/>
-        <v>87.5</v>
-      </c>
-      <c r="D31">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32">
-        <f>COUNTIF(C13:Z13, "O") + COUNTIF(C13:Z13, "P")</f>
-        <v>22</v>
-      </c>
-      <c r="C32">
-        <f t="shared" si="0"/>
-        <v>91.7</v>
-      </c>
-      <c r="D32">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33">
-        <f>COUNTIF(C14:Z14, "O") + COUNTIF(C14:Z14, "P")</f>
-        <v>16</v>
-      </c>
-      <c r="C33">
-        <f t="shared" si="0"/>
-        <v>66.7</v>
-      </c>
-      <c r="D33">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>7</v>
-      </c>
-      <c r="B34">
-        <f>COUNTIF(C15:Z15, "O") + COUNTIF(C15:Z15, "P")</f>
-        <v>22</v>
-      </c>
       <c r="C34">
         <f t="shared" si="0"/>
-        <v>91.7</v>
+        <v>4.2</v>
       </c>
       <c r="D34">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B35">
-        <f>COUNTIF(C16:Z16, "O") + COUNTIF(C16:Z16, "P")</f>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>6</v>
       </c>
       <c r="C35">
         <f t="shared" si="0"/>
-        <v>4.2</v>
+        <v>25</v>
       </c>
       <c r="D35">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B36">
-        <f>COUNTIF(C17:Z17, "O") + COUNTIF(C17:Z17, "P")</f>
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>13</v>
       </c>
       <c r="C36">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>54.2</v>
       </c>
       <c r="D36">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37">
-        <f>COUNTIF(C18:Z18, "O") + COUNTIF(C18:Z18, "P")</f>
+        <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="C37">
-        <f t="shared" si="0"/>
-        <v>54.2</v>
-      </c>
-      <c r="D37">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G18">
-    <sortCondition ref="A2:A18"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G17">
+    <sortCondition ref="A2:A17"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2024AIDataScienceGNRGeneral/Attendance2.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF76CB89-D7C1-44C2-BF92-DF1C4F6FDF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866EACF0-8DB4-441E-AC65-393354719943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AD36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -453,7 +453,7 @@
     <col min="27" max="27" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -538,8 +538,11 @@
       <c r="AC1" s="1">
         <v>45696</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD1" s="1">
+        <v>45703</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -624,8 +627,11 @@
       <c r="AC2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -713,8 +719,11 @@
       <c r="AC3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -802,8 +811,11 @@
       <c r="AC4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -891,8 +903,11 @@
       <c r="AC5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -980,8 +995,11 @@
       <c r="AC6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1069,8 +1087,11 @@
       <c r="AC7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1155,8 +1176,11 @@
       <c r="AC8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1244,8 +1268,11 @@
       <c r="AC9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1333,8 +1360,11 @@
       <c r="AC10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1422,8 +1452,11 @@
       <c r="AC11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1511,8 +1544,11 @@
       <c r="AC12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1600,8 +1636,11 @@
       <c r="AC13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1689,8 +1728,11 @@
       <c r="AC14" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1775,8 +1817,11 @@
       <c r="AC15" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1861,8 +1906,11 @@
       <c r="AC16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -1950,13 +1998,16 @@
       <c r="AC17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="AD17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -1973,7 +2024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -1990,7 +2041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1</v>
       </c>
@@ -2007,7 +2058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>2</v>
       </c>
@@ -2024,7 +2075,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -2041,7 +2092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -2058,7 +2109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -2075,7 +2126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -2092,7 +2143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2109,7 +2160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -2126,7 +2177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -2143,7 +2194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -2160,7 +2211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>

--- a/2024AIDataScienceGNRGeneral/Attendance2.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{866EACF0-8DB4-441E-AC65-393354719943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B271CAC-8118-4E76-BDD9-667BA8B5A304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD36"/>
+  <dimension ref="A1:AE36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -453,7 +453,7 @@
     <col min="27" max="27" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -541,8 +541,11 @@
       <c r="AD1" s="1">
         <v>45703</v>
       </c>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE1" s="1">
+        <v>45717</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -630,8 +633,11 @@
       <c r="AD2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -722,8 +728,11 @@
       <c r="AD3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -814,8 +823,11 @@
       <c r="AD4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -906,8 +918,11 @@
       <c r="AD5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -998,8 +1013,11 @@
       <c r="AD6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1090,8 +1108,11 @@
       <c r="AD7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1179,8 +1200,11 @@
       <c r="AD8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1271,8 +1295,11 @@
       <c r="AD9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1363,8 +1390,11 @@
       <c r="AD10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1455,8 +1485,11 @@
       <c r="AD11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1547,8 +1580,11 @@
       <c r="AD12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1639,8 +1675,11 @@
       <c r="AD13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1731,8 +1770,11 @@
       <c r="AD14" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1820,8 +1862,11 @@
       <c r="AD15" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1909,8 +1954,11 @@
       <c r="AD16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2001,13 +2049,16 @@
       <c r="AD17" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2024,7 +2075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2041,7 +2092,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1</v>
       </c>
@@ -2058,7 +2109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>2</v>
       </c>
@@ -2075,7 +2126,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -2092,7 +2143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -2109,7 +2160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -2126,7 +2177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -2143,7 +2194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2160,7 +2211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -2177,7 +2228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -2194,7 +2245,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -2211,7 +2262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>

--- a/2024AIDataScienceGNRGeneral/Attendance2.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B271CAC-8118-4E76-BDD9-667BA8B5A304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9744B35-DE76-49CD-8CEC-D1484526BB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="31">
   <si>
     <t>Name</t>
   </si>
@@ -440,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE36"/>
+  <dimension ref="A1:AG36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -453,7 +453,7 @@
     <col min="27" max="27" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -544,8 +544,14 @@
       <c r="AE1" s="1">
         <v>45717</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF1" s="1">
+        <v>45724</v>
+      </c>
+      <c r="AG1" s="1">
+        <v>45731</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -636,8 +642,14 @@
       <c r="AE2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -731,8 +743,14 @@
       <c r="AE3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF3" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -826,8 +844,14 @@
       <c r="AE4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -921,8 +945,14 @@
       <c r="AE5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF5" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1016,8 +1046,14 @@
       <c r="AE6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1111,8 +1147,14 @@
       <c r="AE7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF7" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1203,8 +1245,14 @@
       <c r="AE8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF8" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1298,8 +1346,14 @@
       <c r="AE9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF9" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1393,8 +1447,14 @@
       <c r="AE10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1488,8 +1548,14 @@
       <c r="AE11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF11" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -1583,8 +1649,14 @@
       <c r="AE12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1678,8 +1750,14 @@
       <c r="AE13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF13" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1773,8 +1851,14 @@
       <c r="AE14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -1865,8 +1949,14 @@
       <c r="AE15" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1957,8 +2047,14 @@
       <c r="AE16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -2052,13 +2148,19 @@
       <c r="AE17" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF17" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2075,7 +2177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2092,7 +2194,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1</v>
       </c>
@@ -2109,7 +2211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>2</v>
       </c>
@@ -2126,7 +2228,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -2143,7 +2245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -2160,7 +2262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -2177,7 +2279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -2194,7 +2296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2211,7 +2313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -2228,7 +2330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -2245,7 +2347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -2262,7 +2364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>

--- a/2024AIDataScienceGNRGeneral/Attendance2.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9744B35-DE76-49CD-8CEC-D1484526BB08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77687328-D72B-4F05-95C9-542FD4C5EDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="34">
   <si>
     <t>Name</t>
   </si>
@@ -122,6 +122,15 @@
   </si>
   <si>
     <t>Online</t>
+  </si>
+  <si>
+    <t>Divy Shah</t>
+  </si>
+  <si>
+    <t>Jay Parmar</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
   </si>
 </sst>
 </file>
@@ -440,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG36"/>
+  <dimension ref="A1:AH35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -453,7 +462,7 @@
     <col min="27" max="27" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -550,117 +559,126 @@
       <c r="AG1" s="1">
         <v>45731</v>
       </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AH1" s="1">
+        <v>45738</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="N2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="O2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="P2" t="s">
         <v>21</v>
       </c>
       <c r="Q2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="R2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="S2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="T2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="U2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="V2" t="s">
         <v>21</v>
       </c>
       <c r="W2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="X2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Z2" t="s">
-        <v>21</v>
+        <v>15</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>29</v>
       </c>
       <c r="AB2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AC2" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="s">
         <v>21</v>
       </c>
       <c r="AF2" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AG2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AH2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -681,78 +699,81 @@
         <v>9</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="O3" t="s">
         <v>9</v>
       </c>
       <c r="P3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="S3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="U3" t="s">
         <v>9</v>
       </c>
       <c r="V3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="W3" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="X3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Y3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Z3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="s">
         <v>29</v>
       </c>
       <c r="AB3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="s">
         <v>9</v>
       </c>
       <c r="AD3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AE3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AF3" t="s">
         <v>15</v>
       </c>
       <c r="AG3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
@@ -785,16 +806,16 @@
         <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M4" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="N4" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="O4" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="P4" t="s">
         <v>9</v>
@@ -809,16 +830,16 @@
         <v>9</v>
       </c>
       <c r="T4" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="U4" t="s">
         <v>9</v>
       </c>
       <c r="V4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="W4" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="X4" t="s">
         <v>9</v>
@@ -842,18 +863,21 @@
         <v>9</v>
       </c>
       <c r="AE4" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AF4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AG4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AH4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -883,19 +907,19 @@
         <v>9</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="L5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M5" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="N5" t="s">
         <v>9</v>
       </c>
       <c r="O5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="P5" t="s">
         <v>9</v>
@@ -904,7 +928,7 @@
         <v>9</v>
       </c>
       <c r="R5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="S5" t="s">
         <v>9</v>
@@ -919,16 +943,16 @@
         <v>9</v>
       </c>
       <c r="W5" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="X5" t="s">
         <v>9</v>
       </c>
       <c r="Y5" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="s">
         <v>29</v>
@@ -940,10 +964,10 @@
         <v>9</v>
       </c>
       <c r="AD5" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AF5" t="s">
         <v>9</v>
@@ -951,10 +975,13 @@
       <c r="AG5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AH5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
@@ -984,13 +1011,13 @@
         <v>9</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="L6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M6" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="N6" t="s">
         <v>9</v>
@@ -999,19 +1026,19 @@
         <v>9</v>
       </c>
       <c r="P6" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Q6" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="R6" t="s">
         <v>9</v>
       </c>
       <c r="S6" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="T6" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="U6" t="s">
         <v>9</v>
@@ -1023,13 +1050,13 @@
         <v>21</v>
       </c>
       <c r="X6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="s">
         <v>29</v>
@@ -1041,200 +1068,206 @@
         <v>9</v>
       </c>
       <c r="AD6" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AE6" t="s">
         <v>9</v>
       </c>
       <c r="AF6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AG6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AH6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M7" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>9</v>
+      </c>
+      <c r="R7" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" t="s">
+        <v>9</v>
+      </c>
+      <c r="U7" t="s">
+        <v>9</v>
+      </c>
+      <c r="V7" t="s">
+        <v>21</v>
+      </c>
+      <c r="W7" t="s">
+        <v>9</v>
+      </c>
+      <c r="X7" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" t="s">
-        <v>9</v>
-      </c>
-      <c r="O7" t="s">
-        <v>9</v>
-      </c>
-      <c r="P7" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>21</v>
-      </c>
-      <c r="R7" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" t="s">
-        <v>21</v>
-      </c>
-      <c r="T7" t="s">
-        <v>21</v>
-      </c>
-      <c r="U7" t="s">
-        <v>9</v>
-      </c>
-      <c r="V7" t="s">
-        <v>9</v>
-      </c>
-      <c r="W7" t="s">
-        <v>21</v>
-      </c>
-      <c r="X7" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA7" t="s">
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>9</v>
+      </c>
+      <c r="R8" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" t="s">
+        <v>21</v>
+      </c>
+      <c r="U8" t="s">
+        <v>9</v>
+      </c>
+      <c r="V8" t="s">
+        <v>21</v>
+      </c>
+      <c r="W8" t="s">
+        <v>21</v>
+      </c>
+      <c r="X8" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA8" t="s">
         <v>29</v>
       </c>
-      <c r="AB7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>9</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" t="s">
-        <v>9</v>
-      </c>
-      <c r="N8" t="s">
-        <v>9</v>
-      </c>
-      <c r="O8" t="s">
-        <v>9</v>
-      </c>
-      <c r="P8" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>9</v>
-      </c>
-      <c r="R8" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" t="s">
-        <v>9</v>
-      </c>
-      <c r="T8" t="s">
-        <v>9</v>
-      </c>
-      <c r="U8" t="s">
-        <v>9</v>
-      </c>
-      <c r="V8" t="s">
-        <v>21</v>
-      </c>
-      <c r="W8" t="s">
-        <v>9</v>
-      </c>
-      <c r="X8" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>9</v>
-      </c>
       <c r="AB8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AC8" t="s">
         <v>9</v>
@@ -1243,27 +1276,30 @@
         <v>9</v>
       </c>
       <c r="AE8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AF8" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AH8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1284,7 +1320,7 @@
         <v>9</v>
       </c>
       <c r="K9" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="L9" t="s">
         <v>15</v>
@@ -1299,7 +1335,7 @@
         <v>9</v>
       </c>
       <c r="P9" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Q9" t="s">
         <v>9</v>
@@ -1311,13 +1347,13 @@
         <v>9</v>
       </c>
       <c r="T9" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="U9" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="V9" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="W9" t="s">
         <v>21</v>
@@ -1344,18 +1380,21 @@
         <v>9</v>
       </c>
       <c r="AE9" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AF9" t="s">
         <v>9</v>
       </c>
       <c r="AG9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -1382,7 +1421,7 @@
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K10" t="s">
         <v>9</v>
@@ -1400,13 +1439,13 @@
         <v>9</v>
       </c>
       <c r="P10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Q10" t="s">
         <v>9</v>
       </c>
       <c r="R10" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="S10" t="s">
         <v>9</v>
@@ -1415,7 +1454,7 @@
         <v>9</v>
       </c>
       <c r="U10" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="V10" t="s">
         <v>9</v>
@@ -1439,13 +1478,13 @@
         <v>9</v>
       </c>
       <c r="AC10" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AD10" t="s">
         <v>9</v>
       </c>
       <c r="AE10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AF10" t="s">
         <v>9</v>
@@ -1453,16 +1492,19 @@
       <c r="AG10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AH10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
@@ -1474,7 +1516,7 @@
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H11" t="s">
         <v>9</v>
@@ -1483,7 +1525,7 @@
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K11" t="s">
         <v>9</v>
@@ -1507,7 +1549,7 @@
         <v>9</v>
       </c>
       <c r="R11" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="S11" t="s">
         <v>9</v>
@@ -1540,7 +1582,7 @@
         <v>9</v>
       </c>
       <c r="AC11" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="s">
         <v>9</v>
@@ -1549,15 +1591,18 @@
         <v>9</v>
       </c>
       <c r="AF11" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AG11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AH11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
@@ -1572,28 +1617,28 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="H12" t="s">
         <v>9</v>
       </c>
       <c r="I12" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K12" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M12" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="N12" t="s">
         <v>9</v>
@@ -1602,7 +1647,7 @@
         <v>9</v>
       </c>
       <c r="P12" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Q12" t="s">
         <v>9</v>
@@ -1614,7 +1659,7 @@
         <v>9</v>
       </c>
       <c r="T12" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="U12" t="s">
         <v>9</v>
@@ -1626,7 +1671,7 @@
         <v>21</v>
       </c>
       <c r="X12" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="s">
         <v>9</v>
@@ -1650,15 +1695,18 @@
         <v>9</v>
       </c>
       <c r="AF12" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AG12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AH12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
@@ -1673,7 +1721,7 @@
         <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G13" t="s">
         <v>9</v>
@@ -1682,7 +1730,7 @@
         <v>9</v>
       </c>
       <c r="I13" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J13" t="s">
         <v>21</v>
@@ -1691,7 +1739,7 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="M13" t="s">
         <v>15</v>
@@ -1700,10 +1748,10 @@
         <v>9</v>
       </c>
       <c r="O13" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q13" t="s">
         <v>9</v>
@@ -1715,25 +1763,25 @@
         <v>9</v>
       </c>
       <c r="T13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="U13" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="V13" t="s">
         <v>9</v>
       </c>
       <c r="W13" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="X13" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="s">
         <v>9</v>
       </c>
       <c r="Z13" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="s">
         <v>29</v>
@@ -1745,10 +1793,10 @@
         <v>9</v>
       </c>
       <c r="AD13" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AE13" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AF13" t="s">
         <v>9</v>
@@ -1756,34 +1804,37 @@
       <c r="AG13" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="AH13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J14" t="s">
         <v>21</v>
@@ -1792,28 +1843,28 @@
         <v>15</v>
       </c>
       <c r="L14" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M14" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="N14" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="O14" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="P14" t="s">
         <v>15</v>
       </c>
       <c r="Q14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="R14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="S14" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="T14" t="s">
         <v>15</v>
@@ -1822,16 +1873,16 @@
         <v>15</v>
       </c>
       <c r="V14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="W14" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="X14" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="s">
         <v>21</v>
@@ -1852,606 +1903,334 @@
         <v>15</v>
       </c>
       <c r="AF14" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" t="s">
-        <v>21</v>
-      </c>
-      <c r="P15" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>21</v>
-      </c>
-      <c r="R15" t="s">
-        <v>21</v>
-      </c>
-      <c r="S15" t="s">
-        <v>21</v>
-      </c>
-      <c r="T15" t="s">
-        <v>21</v>
-      </c>
-      <c r="U15" t="s">
-        <v>21</v>
-      </c>
-      <c r="V15" t="s">
-        <v>21</v>
-      </c>
-      <c r="W15" t="s">
-        <v>21</v>
-      </c>
-      <c r="X15" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
       </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>9</v>
-      </c>
-      <c r="G16" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" t="s">
-        <v>21</v>
-      </c>
-      <c r="M16" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" t="s">
-        <v>21</v>
-      </c>
-      <c r="P16" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>21</v>
-      </c>
-      <c r="R16" t="s">
-        <v>21</v>
-      </c>
-      <c r="S16" t="s">
-        <v>21</v>
-      </c>
-      <c r="T16" t="s">
-        <v>21</v>
-      </c>
-      <c r="U16" t="s">
-        <v>21</v>
-      </c>
-      <c r="V16" t="s">
-        <v>21</v>
-      </c>
-      <c r="W16" t="s">
-        <v>21</v>
-      </c>
-      <c r="X16" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" t="s">
-        <v>15</v>
-      </c>
-      <c r="J17" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" t="s">
-        <v>15</v>
-      </c>
-      <c r="L17" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" t="s">
-        <v>21</v>
-      </c>
-      <c r="N17" t="s">
-        <v>21</v>
-      </c>
-      <c r="O17" t="s">
-        <v>21</v>
-      </c>
-      <c r="P17" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>15</v>
-      </c>
-      <c r="R17" t="s">
-        <v>15</v>
-      </c>
-      <c r="S17" t="s">
-        <v>21</v>
-      </c>
-      <c r="T17" t="s">
-        <v>15</v>
-      </c>
-      <c r="U17" t="s">
-        <v>15</v>
-      </c>
-      <c r="V17" t="s">
-        <v>15</v>
-      </c>
-      <c r="W17" t="s">
-        <v>21</v>
-      </c>
-      <c r="X17" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AA17" t="s">
-        <v>29</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC17" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="D19" t="s">
+      <c r="AH16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="e">
+        <f>COUNTIF(#REF!, "O") + COUNTIF(#REF!, "P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C19" t="e">
+        <f>ROUND(B19*100/24, 1)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D19" t="e">
+        <f>COUNTIF(#REF!, "O")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B20">
         <f>COUNTIF(C2:Z2, "O") + COUNTIF(C2:Z2, "P")</f>
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C20">
-        <f>ROUND(B20*100/24, 1)</f>
-        <v>12.5</v>
+        <f t="shared" ref="C20:C35" si="0">ROUND(B20*100/24, 1)</f>
+        <v>87.5</v>
       </c>
       <c r="D20">
         <f>COUNTIF(C2:Z2, "O")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B21">
         <f>COUNTIF(C3:Z3, "O") + COUNTIF(C3:Z3, "P")</f>
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C21">
-        <f t="shared" ref="C21:C36" si="0">ROUND(B21*100/24, 1)</f>
-        <v>87.5</v>
+        <f t="shared" si="0"/>
+        <v>70.8</v>
       </c>
       <c r="D21">
         <f>COUNTIF(C3:Z3, "O")</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B22">
+        <v>2</v>
+      </c>
+      <c r="B22" t="e">
+        <f>COUNTIF(#REF!, "O") + COUNTIF(#REF!, "P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C22" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="D22" t="e">
+        <f>COUNTIF(#REF!, "O")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23">
         <f>COUNTIF(C4:Z4, "O") + COUNTIF(C4:Z4, "P")</f>
-        <v>17</v>
-      </c>
-      <c r="C22">
+        <v>21</v>
+      </c>
+      <c r="C23">
         <f t="shared" si="0"/>
-        <v>70.8</v>
-      </c>
-      <c r="D22">
+        <v>87.5</v>
+      </c>
+      <c r="D23">
         <f>COUNTIF(C4:Z4, "O")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24">
+        <f>COUNTIF(C5:Z5, "O") + COUNTIF(C5:Z5, "P")</f>
+        <v>19</v>
+      </c>
+      <c r="C24">
+        <f t="shared" si="0"/>
+        <v>79.2</v>
+      </c>
+      <c r="D24">
+        <f>COUNTIF(C5:Z5, "O")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25">
+        <f>COUNTIF(C6:Z6, "O") + COUNTIF(C6:Z6, "P")</f>
+        <v>18</v>
+      </c>
+      <c r="C25">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="D25">
+        <f>COUNTIF(C6:Z6, "O")</f>
         <v>2</v>
       </c>
-      <c r="B23" t="e">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <f>COUNTIF(C7:Z7, "O") + COUNTIF(C7:Z7, "P")</f>
+        <v>22</v>
+      </c>
+      <c r="C26">
+        <f t="shared" si="0"/>
+        <v>91.7</v>
+      </c>
+      <c r="D26">
+        <f>COUNTIF(C7:Z7, "O")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <f>COUNTIF(C8:Z8, "O") + COUNTIF(C8:Z8, "P")</f>
+        <v>18</v>
+      </c>
+      <c r="C27">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+      <c r="D27">
+        <f>COUNTIF(C8:Z8, "O")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28">
+        <f>COUNTIF(C9:Z9, "O") + COUNTIF(C9:Z9, "P")</f>
+        <v>22</v>
+      </c>
+      <c r="C28">
+        <f t="shared" si="0"/>
+        <v>91.7</v>
+      </c>
+      <c r="D28">
+        <f>COUNTIF(C9:Z9, "O")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29">
+        <f>COUNTIF(C10:Z10, "O") + COUNTIF(C10:Z10, "P")</f>
+        <v>21</v>
+      </c>
+      <c r="C29">
+        <f t="shared" si="0"/>
+        <v>87.5</v>
+      </c>
+      <c r="D29">
+        <f>COUNTIF(C10:Z10, "O")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30">
+        <f>COUNTIF(C11:Z11, "O") + COUNTIF(C11:Z11, "P")</f>
+        <v>22</v>
+      </c>
+      <c r="C30">
+        <f t="shared" si="0"/>
+        <v>91.7</v>
+      </c>
+      <c r="D30">
+        <f>COUNTIF(C11:Z11, "O")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31">
+        <f>COUNTIF(C12:Z12, "O") + COUNTIF(C12:Z12, "P")</f>
+        <v>16</v>
+      </c>
+      <c r="C31">
+        <f t="shared" si="0"/>
+        <v>66.7</v>
+      </c>
+      <c r="D31">
+        <f>COUNTIF(C12:Z12, "O")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32">
+        <f>COUNTIF(C13:Z13, "O") + COUNTIF(C13:Z13, "P")</f>
+        <v>22</v>
+      </c>
+      <c r="C32">
+        <f t="shared" si="0"/>
+        <v>91.7</v>
+      </c>
+      <c r="D32">
+        <f>COUNTIF(C13:Z13, "O")</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="e">
         <f>COUNTIF(#REF!, "O") + COUNTIF(#REF!, "P")</f>
         <v>#REF!</v>
       </c>
-      <c r="C23" t="e">
+      <c r="C33" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="D23" t="e">
+      <c r="D33" t="e">
         <f>COUNTIF(#REF!, "O")</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24">
-        <f t="shared" ref="B24:B36" si="1">COUNTIF(C5:Z5, "O") + COUNTIF(C5:Z5, "P")</f>
-        <v>21</v>
-      </c>
-      <c r="C24">
-        <f t="shared" si="0"/>
-        <v>87.5</v>
-      </c>
-      <c r="D24">
-        <f t="shared" ref="D24:D36" si="2">COUNTIF(C5:Z5, "O")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25">
-        <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-      <c r="C25">
-        <f t="shared" si="0"/>
-        <v>79.2</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="C26">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="C27">
-        <f t="shared" si="0"/>
-        <v>91.7</v>
-      </c>
-      <c r="D27">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="C28">
-        <f t="shared" si="0"/>
-        <v>75</v>
-      </c>
-      <c r="D28">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="C29">
-        <f t="shared" si="0"/>
-        <v>91.7</v>
-      </c>
-      <c r="D29">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-      <c r="C30">
-        <f t="shared" si="0"/>
-        <v>87.5</v>
-      </c>
-      <c r="D30">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="C31">
-        <f t="shared" si="0"/>
-        <v>91.7</v>
-      </c>
-      <c r="D31">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="C32">
-        <f t="shared" si="0"/>
-        <v>66.7</v>
-      </c>
-      <c r="D32">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>7</v>
-      </c>
-      <c r="B33">
-        <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="C33">
-        <f t="shared" si="0"/>
-        <v>91.7</v>
-      </c>
-      <c r="D33">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-    </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C34">
+        <v>14</v>
+      </c>
+      <c r="B34" t="e">
+        <f>COUNTIF(#REF!, "O") + COUNTIF(#REF!, "P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C34" t="e">
         <f t="shared" si="0"/>
-        <v>4.2</v>
-      </c>
-      <c r="D34">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>#REF!</v>
+      </c>
+      <c r="D34" t="e">
+        <f>COUNTIF(#REF!, "O")</f>
+        <v>#REF!</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B35">
-        <f t="shared" si="1"/>
-        <v>6</v>
+        <f t="shared" ref="B35" si="1">COUNTIF(C14:Z14, "O") + COUNTIF(C14:Z14, "P")</f>
+        <v>13</v>
       </c>
       <c r="C35">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>54.2</v>
       </c>
       <c r="D35">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B36">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="D35" si="2">COUNTIF(C14:Z14, "O")</f>
         <v>13</v>
       </c>
-      <c r="C36">
-        <f t="shared" si="0"/>
-        <v>54.2</v>
-      </c>
-      <c r="D36">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G17">
-    <sortCondition ref="A2:A17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G14">
+    <sortCondition ref="A2:A14"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2024AIDataScienceGNRGeneral/Attendance2.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77687328-D72B-4F05-95C9-542FD4C5EDC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3502C3A8-6136-4DD2-9F75-C0546BC267D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="34">
   <si>
     <t>Name</t>
   </si>
@@ -449,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH35"/>
+  <dimension ref="A1:AI35"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -462,7 +462,7 @@
     <col min="27" max="27" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -562,8 +562,11 @@
       <c r="AH1" s="1">
         <v>45738</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI1" s="1">
+        <v>45745</v>
+      </c>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -666,8 +669,11 @@
       <c r="AH2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -770,8 +776,11 @@
       <c r="AH3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -874,8 +883,11 @@
       <c r="AH4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -978,8 +990,11 @@
       <c r="AH5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1082,8 +1097,11 @@
       <c r="AH6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1183,8 +1201,11 @@
       <c r="AH7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1287,8 +1308,11 @@
       <c r="AH8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1391,8 +1415,11 @@
       <c r="AH9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1495,8 +1522,11 @@
       <c r="AH10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1599,8 +1629,11 @@
       <c r="AH11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1703,8 +1736,11 @@
       <c r="AH12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1807,8 +1843,11 @@
       <c r="AH13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1911,8 +1950,11 @@
       <c r="AH14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1922,8 +1964,11 @@
       <c r="AH15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="AI15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -1931,6 +1976,9 @@
         <v>19</v>
       </c>
       <c r="AH16" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI16" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2012,7 +2060,7 @@
         <v>8</v>
       </c>
       <c r="B23">
-        <f>COUNTIF(C4:Z4, "O") + COUNTIF(C4:Z4, "P")</f>
+        <f t="shared" ref="B23:B32" si="1">COUNTIF(C4:Z4, "O") + COUNTIF(C4:Z4, "P")</f>
         <v>21</v>
       </c>
       <c r="C23">
@@ -2020,7 +2068,7 @@
         <v>87.5</v>
       </c>
       <c r="D23">
-        <f>COUNTIF(C4:Z4, "O")</f>
+        <f t="shared" ref="D23:D32" si="2">COUNTIF(C4:Z4, "O")</f>
         <v>1</v>
       </c>
     </row>
@@ -2029,7 +2077,7 @@
         <v>4</v>
       </c>
       <c r="B24">
-        <f>COUNTIF(C5:Z5, "O") + COUNTIF(C5:Z5, "P")</f>
+        <f t="shared" si="1"/>
         <v>19</v>
       </c>
       <c r="C24">
@@ -2037,7 +2085,7 @@
         <v>79.2</v>
       </c>
       <c r="D24">
-        <f>COUNTIF(C5:Z5, "O")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2046,7 +2094,7 @@
         <v>3</v>
       </c>
       <c r="B25">
-        <f>COUNTIF(C6:Z6, "O") + COUNTIF(C6:Z6, "P")</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="C25">
@@ -2054,7 +2102,7 @@
         <v>75</v>
       </c>
       <c r="D25">
-        <f>COUNTIF(C6:Z6, "O")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -2063,7 +2111,7 @@
         <v>11</v>
       </c>
       <c r="B26">
-        <f>COUNTIF(C7:Z7, "O") + COUNTIF(C7:Z7, "P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="C26">
@@ -2071,7 +2119,7 @@
         <v>91.7</v>
       </c>
       <c r="D26">
-        <f>COUNTIF(C7:Z7, "O")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -2080,7 +2128,7 @@
         <v>24</v>
       </c>
       <c r="B27">
-        <f>COUNTIF(C8:Z8, "O") + COUNTIF(C8:Z8, "P")</f>
+        <f t="shared" si="1"/>
         <v>18</v>
       </c>
       <c r="C27">
@@ -2088,7 +2136,7 @@
         <v>75</v>
       </c>
       <c r="D27">
-        <f>COUNTIF(C8:Z8, "O")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2097,7 +2145,7 @@
         <v>13</v>
       </c>
       <c r="B28">
-        <f>COUNTIF(C9:Z9, "O") + COUNTIF(C9:Z9, "P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="C28">
@@ -2105,7 +2153,7 @@
         <v>91.7</v>
       </c>
       <c r="D28">
-        <f>COUNTIF(C9:Z9, "O")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -2114,7 +2162,7 @@
         <v>12</v>
       </c>
       <c r="B29">
-        <f>COUNTIF(C10:Z10, "O") + COUNTIF(C10:Z10, "P")</f>
+        <f t="shared" si="1"/>
         <v>21</v>
       </c>
       <c r="C29">
@@ -2122,7 +2170,7 @@
         <v>87.5</v>
       </c>
       <c r="D29">
-        <f>COUNTIF(C10:Z10, "O")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -2131,7 +2179,7 @@
         <v>5</v>
       </c>
       <c r="B30">
-        <f>COUNTIF(C11:Z11, "O") + COUNTIF(C11:Z11, "P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="C30">
@@ -2139,7 +2187,7 @@
         <v>91.7</v>
       </c>
       <c r="D30">
-        <f>COUNTIF(C11:Z11, "O")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -2148,7 +2196,7 @@
         <v>6</v>
       </c>
       <c r="B31">
-        <f>COUNTIF(C12:Z12, "O") + COUNTIF(C12:Z12, "P")</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="C31">
@@ -2156,7 +2204,7 @@
         <v>66.7</v>
       </c>
       <c r="D31">
-        <f>COUNTIF(C12:Z12, "O")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
@@ -2165,7 +2213,7 @@
         <v>7</v>
       </c>
       <c r="B32">
-        <f>COUNTIF(C13:Z13, "O") + COUNTIF(C13:Z13, "P")</f>
+        <f t="shared" si="1"/>
         <v>22</v>
       </c>
       <c r="C32">
@@ -2173,7 +2221,7 @@
         <v>91.7</v>
       </c>
       <c r="D32">
-        <f>COUNTIF(C13:Z13, "O")</f>
+        <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
@@ -2216,7 +2264,7 @@
         <v>16</v>
       </c>
       <c r="B35">
-        <f t="shared" ref="B35" si="1">COUNTIF(C14:Z14, "O") + COUNTIF(C14:Z14, "P")</f>
+        <f t="shared" ref="B35" si="3">COUNTIF(C14:Z14, "O") + COUNTIF(C14:Z14, "P")</f>
         <v>13</v>
       </c>
       <c r="C35">
@@ -2224,7 +2272,7 @@
         <v>54.2</v>
       </c>
       <c r="D35">
-        <f t="shared" ref="D35" si="2">COUNTIF(C14:Z14, "O")</f>
+        <f t="shared" ref="D35" si="4">COUNTIF(C14:Z14, "O")</f>
         <v>13</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRGeneral/Attendance2.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3502C3A8-6136-4DD2-9F75-C0546BC267D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBEC98A-1DBD-4AEB-8FE8-342B7F05E187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="36">
   <si>
     <t>Name</t>
   </si>
@@ -131,6 +131,12 @@
   </si>
   <si>
     <t>Ahmedabad</t>
+  </si>
+  <si>
+    <t>Vraj Shah</t>
+  </si>
+  <si>
+    <t>Vadodara</t>
   </si>
 </sst>
 </file>
@@ -449,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI35"/>
+  <dimension ref="A1:AJ36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -462,7 +468,7 @@
     <col min="27" max="27" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -565,8 +571,11 @@
       <c r="AI1" s="1">
         <v>45745</v>
       </c>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ1" s="1">
+        <v>45752</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -672,8 +681,11 @@
       <c r="AI2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -779,8 +791,11 @@
       <c r="AI3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -886,8 +901,11 @@
       <c r="AI4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -993,8 +1011,11 @@
       <c r="AI5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1100,8 +1121,11 @@
       <c r="AI6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1204,8 +1228,11 @@
       <c r="AI7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1311,8 +1338,11 @@
       <c r="AI8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1418,8 +1448,11 @@
       <c r="AI9" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1525,8 +1558,11 @@
       <c r="AI10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1632,8 +1668,11 @@
       <c r="AI11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1739,8 +1778,11 @@
       <c r="AI12" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1846,8 +1888,11 @@
       <c r="AI13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1953,8 +1998,11 @@
       <c r="AI14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -1967,8 +2015,11 @@
       <c r="AI15" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="AJ15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -1981,270 +2032,267 @@
       <c r="AI16" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="D18" t="s">
+      <c r="AJ16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="D19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>22</v>
       </c>
-      <c r="B19" t="e">
+      <c r="B20" t="e">
         <f>COUNTIF(#REF!, "O") + COUNTIF(#REF!, "P")</f>
         <v>#REF!</v>
       </c>
-      <c r="C19" t="e">
-        <f>ROUND(B19*100/24, 1)</f>
+      <c r="C20" t="e">
+        <f>ROUND(B20*100/24, 1)</f>
         <v>#REF!</v>
       </c>
-      <c r="D19" t="e">
+      <c r="D20" t="e">
         <f>COUNTIF(#REF!, "O")</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>10</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <f>COUNTIF(C2:Z2, "O") + COUNTIF(C2:Z2, "P")</f>
         <v>21</v>
       </c>
-      <c r="C20">
-        <f t="shared" ref="C20:C35" si="0">ROUND(B20*100/24, 1)</f>
+      <c r="C21">
+        <f t="shared" ref="C21:C36" si="0">ROUND(B21*100/24, 1)</f>
         <v>87.5</v>
       </c>
-      <c r="D20">
+      <c r="D21">
         <f>COUNTIF(C2:Z2, "O")</f>
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>1</v>
       </c>
-      <c r="B21">
+      <c r="B22">
         <f>COUNTIF(C3:Z3, "O") + COUNTIF(C3:Z3, "P")</f>
         <v>17</v>
       </c>
-      <c r="C21">
+      <c r="C22">
         <f t="shared" si="0"/>
         <v>70.8</v>
       </c>
-      <c r="D21">
+      <c r="D22">
         <f>COUNTIF(C3:Z3, "O")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>2</v>
       </c>
-      <c r="B22" t="e">
+      <c r="B23" t="e">
         <f>COUNTIF(#REF!, "O") + COUNTIF(#REF!, "P")</f>
         <v>#REF!</v>
       </c>
-      <c r="C22" t="e">
+      <c r="C23" t="e">
         <f t="shared" si="0"/>
         <v>#REF!</v>
       </c>
-      <c r="D22" t="e">
+      <c r="D23" t="e">
         <f>COUNTIF(#REF!, "O")</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>8</v>
       </c>
-      <c r="B23">
-        <f t="shared" ref="B23:B32" si="1">COUNTIF(C4:Z4, "O") + COUNTIF(C4:Z4, "P")</f>
-        <v>21</v>
-      </c>
-      <c r="C23">
+      <c r="B24">
+        <f t="shared" ref="B24:B33" si="1">COUNTIF(C4:Z4, "O") + COUNTIF(C4:Z4, "P")</f>
+        <v>21</v>
+      </c>
+      <c r="C24">
         <f t="shared" si="0"/>
         <v>87.5</v>
       </c>
-      <c r="D23">
-        <f t="shared" ref="D23:D32" si="2">COUNTIF(C4:Z4, "O")</f>
+      <c r="D24">
+        <f t="shared" ref="D24:D33" si="2">COUNTIF(C4:Z4, "O")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>4</v>
       </c>
-      <c r="B24">
+      <c r="B25">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="C24">
+      <c r="C25">
         <f t="shared" si="0"/>
         <v>79.2</v>
       </c>
-      <c r="D24">
+      <c r="D25">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>3</v>
       </c>
-      <c r="B25">
+      <c r="B26">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="C25">
+      <c r="C26">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="D25">
+      <c r="D26">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>11</v>
       </c>
-      <c r="B26">
+      <c r="B27">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="C26">
+      <c r="C27">
         <f t="shared" si="0"/>
         <v>91.7</v>
       </c>
-      <c r="D26">
+      <c r="D27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>24</v>
       </c>
-      <c r="B27">
+      <c r="B28">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="D27">
+      <c r="D28">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>13</v>
       </c>
-      <c r="B28">
+      <c r="B29">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="C28">
+      <c r="C29">
         <f t="shared" si="0"/>
         <v>91.7</v>
       </c>
-      <c r="D28">
+      <c r="D29">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>12</v>
       </c>
-      <c r="B29">
+      <c r="B30">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="C29">
+      <c r="C30">
         <f t="shared" si="0"/>
         <v>87.5</v>
       </c>
-      <c r="D29">
+      <c r="D30">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="C30">
+      <c r="C31">
         <f t="shared" si="0"/>
         <v>91.7</v>
       </c>
-      <c r="D30">
+      <c r="D31">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>6</v>
       </c>
-      <c r="B31">
+      <c r="B32">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="C31">
+      <c r="C32">
         <f t="shared" si="0"/>
         <v>66.7</v>
       </c>
-      <c r="D31">
+      <c r="D32">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>7</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="C32">
+      <c r="C33">
         <f t="shared" si="0"/>
         <v>91.7</v>
       </c>
-      <c r="D32">
+      <c r="D33">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B33" t="e">
-        <f>COUNTIF(#REF!, "O") + COUNTIF(#REF!, "P")</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C33" t="e">
-        <f t="shared" si="0"/>
-        <v>#REF!</v>
-      </c>
-      <c r="D33" t="e">
-        <f>COUNTIF(#REF!, "O")</f>
-        <v>#REF!</v>
-      </c>
-    </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B34" t="e">
         <f>COUNTIF(#REF!, "O") + COUNTIF(#REF!, "P")</f>
@@ -2261,18 +2309,35 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" t="e">
+        <f>COUNTIF(#REF!, "O") + COUNTIF(#REF!, "P")</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C35" t="e">
+        <f t="shared" si="0"/>
+        <v>#REF!</v>
+      </c>
+      <c r="D35" t="e">
+        <f>COUNTIF(#REF!, "O")</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>16</v>
       </c>
-      <c r="B35">
-        <f t="shared" ref="B35" si="3">COUNTIF(C14:Z14, "O") + COUNTIF(C14:Z14, "P")</f>
+      <c r="B36">
+        <f t="shared" ref="B36" si="3">COUNTIF(C14:Z14, "O") + COUNTIF(C14:Z14, "P")</f>
         <v>13</v>
       </c>
-      <c r="C35">
+      <c r="C36">
         <f t="shared" si="0"/>
         <v>54.2</v>
       </c>
-      <c r="D35">
-        <f t="shared" ref="D35" si="4">COUNTIF(C14:Z14, "O")</f>
+      <c r="D36">
+        <f t="shared" ref="D36" si="4">COUNTIF(C14:Z14, "O")</f>
         <v>13</v>
       </c>
     </row>

--- a/2024AIDataScienceGNRGeneral/Attendance2.xlsx
+++ b/2024AIDataScienceGNRGeneral/Attendance2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DBEC98A-1DBD-4AEB-8FE8-342B7F05E187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FA6955-925B-47BC-8F99-364F9D1D8BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="36">
   <si>
     <t>Name</t>
   </si>
@@ -455,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AJ36"/>
+  <dimension ref="A1:AK36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
@@ -468,7 +468,7 @@
     <col min="27" max="27" width="24.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -574,8 +574,11 @@
       <c r="AJ1" s="1">
         <v>45752</v>
       </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK1" s="1">
+        <v>45759</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -684,8 +687,11 @@
       <c r="AJ2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -794,8 +800,11 @@
       <c r="AJ3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -904,8 +913,11 @@
       <c r="AJ4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1014,8 +1026,11 @@
       <c r="AJ5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1124,8 +1139,11 @@
       <c r="AJ6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1231,8 +1249,11 @@
       <c r="AJ7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1341,8 +1362,11 @@
       <c r="AJ8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1451,8 +1475,11 @@
       <c r="AJ9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1561,8 +1588,11 @@
       <c r="AJ10" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -1671,8 +1701,11 @@
       <c r="AJ11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1781,8 +1814,11 @@
       <c r="AJ12" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1891,8 +1927,11 @@
       <c r="AJ13" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -2001,8 +2040,11 @@
       <c r="AJ14" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -2018,8 +2060,11 @@
       <c r="AJ15" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -2035,8 +2080,11 @@
       <c r="AJ16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -2046,13 +2094,16 @@
       <c r="AJ17" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="AK17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2069,7 +2120,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2086,7 +2137,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1</v>
       </c>
@@ -2103,7 +2154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>2</v>
       </c>
@@ -2120,7 +2171,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -2137,7 +2188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -2154,7 +2205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -2171,7 +2222,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -2188,7 +2239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2205,7 +2256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -2222,7 +2273,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -2239,7 +2290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -2256,7 +2307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>6</v>
       </c>
